--- a/diseases/d001/2015-2019.xlsx
+++ b/diseases/d001/2015-2019.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2493,9 +2487,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3529,9 +3520,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4553,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5749,9 +5734,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6785,9 +6767,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7821,9 +7800,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9005,9 +8981,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10041,9 +10014,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -11077,9 +11047,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12261,9 +12228,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13297,9 +13261,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -14333,9 +14294,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14877,9 +14835,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15913,9 +15868,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16949,9 +16901,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -18133,9 +18082,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -19169,9 +19115,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -20205,9 +20148,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -21537,9 +21477,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -22573,9 +22510,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -23609,9 +23543,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -24793,9 +24724,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25977,9 +25905,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -27161,9 +27086,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -28345,9 +28267,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -28741,9 +28660,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -29777,9 +29693,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -30813,9 +30726,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -31997,9 +31907,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -33033,9 +32940,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -34069,9 +33973,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -35253,9 +35154,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -36289,9 +36187,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -37473,9 +37368,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -38509,9 +38401,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -39545,9 +39434,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -40729,9 +40615,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -41765,9 +41648,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -42161,9 +42041,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -43197,9 +43074,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -44233,9 +44107,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -45417,9 +45288,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -46453,9 +46321,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -47785,9 +47650,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -48821,9 +48683,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -49857,9 +49716,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -51041,9 +50897,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -52225,9 +52078,6 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0</v>
       </c>
@@ -53409,9 +53259,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -54593,9 +54440,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -55777,9 +55621,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -56173,9 +56014,6 @@
       <c r="O373" t="n">
         <v>0</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0</v>
       </c>
@@ -57357,9 +57195,6 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0</v>
       </c>
@@ -58393,9 +58228,6 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0</v>
       </c>
@@ -59577,9 +59409,6 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
@@ -60761,9 +60590,6 @@
       <c r="O404" t="n">
         <v>0</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0</v>
       </c>
@@ -61945,9 +61771,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -62981,9 +62804,6 @@
       <c r="O419" t="n">
         <v>0</v>
       </c>
-      <c r="Q419" t="n">
-        <v>0</v>
-      </c>
       <c r="R419" t="n">
         <v>0</v>
       </c>
@@ -64017,9 +63837,6 @@
       <c r="O426" t="n">
         <v>0</v>
       </c>
-      <c r="Q426" t="n">
-        <v>0</v>
-      </c>
       <c r="R426" t="n">
         <v>0</v>
       </c>
@@ -65349,9 +65166,6 @@
       <c r="O435" t="n">
         <v>0</v>
       </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
       <c r="R435" t="n">
         <v>0</v>
       </c>
@@ -66385,9 +66199,6 @@
       <c r="O442" t="n">
         <v>0</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0</v>
       </c>
@@ -67569,9 +67380,6 @@
       <c r="O450" t="n">
         <v>0</v>
       </c>
-      <c r="Q450" t="n">
-        <v>0</v>
-      </c>
       <c r="R450" t="n">
         <v>0</v>
       </c>
@@ -68751,9 +68559,6 @@
         <v>0</v>
       </c>
       <c r="O458" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q458" t="n">
         <v>0</v>
       </c>
       <c r="R458" t="n">
